--- a/Книги/Рейтинг книг по темам.xlsx
+++ b/Книги/Рейтинг книг по темам.xlsx
@@ -527,19 +527,19 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="C2" s="2" t="n">
         <v>63</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>55</v>
@@ -552,22 +552,22 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>109</v>
+        <v>120</v>
       </c>
       <c r="C3" s="2" t="n">
         <v>55</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="G3" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4">
@@ -577,22 +577,22 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="C4" s="2" t="n">
         <v>64</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -602,19 +602,19 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C5" s="2" t="n">
         <v>14</v>
       </c>
       <c r="D5" s="2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>15</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>5</v>
@@ -627,19 +627,19 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C6" s="2" t="n">
         <v>12</v>
       </c>
       <c r="D6" s="2" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>0</v>
@@ -652,19 +652,19 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="2" t="n">
         <v>10</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>9</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>1</v>
@@ -677,19 +677,19 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C8" s="2" t="n">
         <v>6</v>
       </c>
       <c r="D8" s="2" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>2</v>
@@ -752,19 +752,19 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C11" s="2" t="n">
         <v>4</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>1</v>
@@ -1005,7 +1005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1165,6 +1165,36 @@
       <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Массовый жанр без научной верификации</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Год, прожитый правильно: 52 шага к здоровому образу жизни</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Блюменталь Бретт</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>52 недели здоровых привычек [ваш список]</t>
         </is>
       </c>
     </row>
@@ -1263,7 +1293,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F147"/>
+  <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5686,6 +5716,66 @@
         </is>
       </c>
     </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>Рэй Далио: Принципы. Жизнь и работа</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Далио Рэй</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Бестселлер основателя Bridgewater о принципах принятия решений [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>Экономика всего. Институты и общество: жизнь по правилам и без</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Александр Аузан</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Аузан — известный российский экономист об институтах [ваш список]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5697,7 +5787,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F110"/>
+  <dimension ref="A1:F121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -9010,6 +9100,336 @@
         </is>
       </c>
     </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Закон успеха</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Наполеон Хилл</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Хилл — классический 16-томный курс успеха, дополняет «Думай и богатей» [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>111</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Привычки на миллион. Проверенные способы удвоить и утроить свой доход</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Брайан Трейси</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Трейси — прикладные привычки роста дохода [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>112</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Основы теории игр (серия «Знания, которые не займут много места» / «Для тех, кто хочет все успеть»)</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Научпоп-обзор теории игр, два издания одной серии [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>113</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Как лгать при помощи статистики</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Дарелл Хафф</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Классика 1954 г. о манипуляции статистикой, must-read критического мышления [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>114</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Цель вашей жизни: Как обрести мечту и не сбиться с пути</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Кови Стивен Р.</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Кови — о цели и смысле, дополняет «7 навыков» [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>115</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Безграничная память. Запоминай быстро, помни долго</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Кевин Хорсли</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Практические техники запоминания [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>116</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Дворец памяти: 70 задач для развития памяти</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Гарет Мур</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Тренажёр памяти, 70 задач [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>117</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Тренажер мозга. Продвинутый уровень: 40 дней интенсивных тренировок</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Гарет Мур</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Интенсивный 40-дневный тренинг мозга [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>118</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Советский тренажер для ума. Высокоэффективные тренировки памяти и внимания</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Антон Могучий</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Тренировки памяти и внимания [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>119</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Низкий</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Тренажер утренних привычек: Дневник-помощник</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Дневник-практикум привычек, формат не классическая книга [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>120</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>ТРИЗ. Как решить любую проблему</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Методология решения изобретательских задач [ваш список]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9021,7 +9441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F96"/>
+  <dimension ref="A1:F111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -11914,6 +12334,456 @@
         </is>
       </c>
     </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Когда мысли лезут в голову. Избавься от навязчивых состояний ОКР</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Прибытков Алексей Александрович</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Практическое руководство по ОКР и навязчивым мыслям [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Хватит быть удобным. Как научиться говорить «НЕТ» без угрызений совести</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Захариадис Деймон</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Тема личных границ и отказа [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Как стать несчастным без посторонней помощи</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Вацлавик Павел</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ироничная классика Пало-Альто о самосаботаже [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Удалить и забыть: как перестать думать о манипуляторах и других токсичных людях</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Сугавара Митихито</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Японский подход к токсичным людям [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Лучше плохо, чем никак. Как обмануть перфекционизм</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Захариадис Деймон</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Практика против перфекционизма [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Не мешай себе жить. Как справиться с проявлениями саморазрушительного поведения</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Гоулстон Марк</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Гоулстон — о саморазрушительных паттернах [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Игры, в которые играют люди</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Берн Эрик</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Классика транзактного анализа (Берн) [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Как перестать беспокоиться и начать жить</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Дейл Карнеги</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Классика Карнеги об управлении тревогой [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>104</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Сила спокойствия. Внутренний стоицизм как путь к развитию и успеху</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Холидей Райан</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Холидей — практический стоицизм [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>105</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Дневник стоика. 366 вопросов к себе</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Холидей Райан, Хансельман Стивен</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Стоический практикум на каждый день [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>106</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Хватит быть славным парнем! Как добиться желаемого в любви, работе и жизни</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Гловер Роберт</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>О созависимости и «хорошести» [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>107</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Я вижу, о чем вы думаете</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Наварро Джо, Карлинс Марвин</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>Язык тела от экс-агента ФБР [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>108</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Вижу вас насквозь 2.0. Как «читать» людей</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Евгений Спирица</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>Профайлинг на практике [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>109</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Невроз и личностный рост: борьба за самореализацию</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Хорни Карен</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Классика неофрейдизма (Хорни) [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>110</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Низкий</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Никогда не спорьте с идиотами!</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Неполное название/неоднозначный источник — уточнить автора [ваш список]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -11925,7 +12795,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13348,12 +14218,756 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Монстр продаж. Как чертовски хорошо продавать и богатеть</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Рызов Игорь Романович</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Рызов — переговоры и продажи, российский рынок [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Кремлевская школа переговоров</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Рызов Игорь Романович</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Рызов — известная методика жёстких переговоров [ваш список]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="28" customWidth="1" min="5" max="5"/>
+    <col width="65" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>№</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Приоритет</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Статус</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Книга</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Автор</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Почему / комментарий</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C2" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>ia-slysu-vas-naskvoz</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>Марк Гоулстон — один из самых известных нон-фикшн по слушанию/эмпатии</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>хьюстон тереза - обратная связь как сказать все что думаешь</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Тереза Хьюстон — признанная книга по эффективной обратной связи</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>юри уильям - мы можем договориться стратегии разрешения слож</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Уильям Юри — топ по теме разрешения конфликтов</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Договориться можно обо всем!</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Нашёл 2 FB2 в папке загрузок:</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Гэвин Кеннеди — классика переговоров [из истории проекта]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>golos-99-upraznenii-dlia-trenirovki-razvitiia-i-soversenstvo</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Практикум по постановке голоса</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>govori-krasivo-i-uverenno-postanovka-golosa-i-reci</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Прикладной курс по голосу и речи</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>iskusstvo-legkogo-obshheniia-ot-nelovkix-pauz-k-besede-na-li</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Практическое пособие по small talk</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>kak-razgovarivat-s-kem-ugodno-uverennoe-obshhenie-v-liuboi-s</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Практическое пособие по уверенному общению</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>net-i-tocka-iskusstvo-govorit-net-bez-cuvstva-viny</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Практическая тема личных границ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>гоулстон марк - умение слушать осознанно</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Гоулстон — дубль темы с книгой выше</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>демиденко артем - переговоры на грани как выигрывать сложные</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Демиденко — массовый автор, обзорная книга по переговорам</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>кинг патрик - как быть веселым остроумным и креативным</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Патрик Кинг — лёгкий практический жанр</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>кинг патрик - справочник мастера харизмы 174 поведенческих п</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>Патрик Кинг — практический сборник приёмов харизмы</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Харизма речи. Воркбук для развития магнетизма</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Зиннатуллин Айнур Мансурович</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Практикум харизматичной речи [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Харизма голоса. Как говорить красиво и излучать уверенность</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Зиннатуллин Айнур Мансурович</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Постановка голоса и уверенность [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Камасутра для оратора</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Гандапас Радислав Иванович</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Гандапас — классик российского ораторства [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Речевая самооборона</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Хоменко Руслан Николаевич, Пожарская Александра</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Защита от словесных манипуляций [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Искусство речи</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Петрова Анна Николаевна</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Постановка речи и дикция [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Переговоры. Полный курс</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Гэвин Кеннеди</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Кеннеди — большой учебник переговоров; рядом есть «Договориться можно обо всем» того же автора [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Говорить «нет», не испытывая чувства вины</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Шейнов Виктор Павлович</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Личные границы; тематически близко «Нет и точка» [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Красивый голос и четкая дикция за 30 дней. Только практика</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Плешаков-Качалин Кирилл</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>30-дневный практикум дикции [ваш список]</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -13418,7 +15032,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>ia-slysu-vas-naskvoz</t>
+          <t>arhangelskii g- taim-draiv ipod</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -13428,7 +15042,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Марк Гоулстон — один из самых известных нон-фикшн по слушанию/эмпатии</t>
+          <t>Глеб Архангельский — ключевое издание по тайм-менеджменту</t>
         </is>
       </c>
     </row>
@@ -13448,7 +15062,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>хьюстон тереза - обратная связь как сказать все что думаешь</t>
+          <t>kak-privesti-dela-v-poriadok-iskusstvo-produktivnosti-bez-st</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -13458,7 +15072,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Тереза Хьюстон — признанная книга по эффективной обратной связи</t>
+          <t>Дэвид Аллен — главная книга по системе GTD</t>
         </is>
       </c>
     </row>
@@ -13478,7 +15092,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>юри уильям - мы можем договориться стратегии разрешения слож</t>
+          <t>kak-razobratsia-s-delami</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -13488,7 +15102,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Уильям Юри — топ по теме разрешения конфликтов</t>
+          <t>Дэвид Аллен — ещё одно издание GTD</t>
         </is>
       </c>
     </row>
@@ -13501,24 +15115,24 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>Нет</t>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Есть</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Договориться можно обо всем!</t>
+          <t>архангельский глеб - время большая книга тайм-менеджмента</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Нашёл 2 FB2 в папке загрузок:</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Гэвин Кеннеди — классика переговоров [из истории проекта]</t>
+          <t>Глеб Архангельский — главный русскоязычный автор темы</t>
         </is>
       </c>
     </row>
@@ -13526,9 +15140,9 @@
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Высокий</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -13538,7 +15152,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>golos-99-upraznenii-dlia-trenirovki-razvitiia-i-soversenstvo</t>
+          <t>архангельский глеб - организация времени от личной эффективн</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -13548,7 +15162,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Практикум по постановке голоса</t>
+          <t>Архангельский — расширенная версия методологии</t>
         </is>
       </c>
     </row>
@@ -13556,9 +15170,9 @@
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>Высокий</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -13568,7 +15182,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>govori-krasivo-i-uverenno-postanovka-golosa-i-reci</t>
+          <t>фрайд джейсон - не сходите с ума на работе</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -13578,7 +15192,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Прикладной курс по голосу и речи</t>
+          <t>Джейсон Фрайд — влиятельная книга о фокусе в работе</t>
         </is>
       </c>
     </row>
@@ -13586,9 +15200,9 @@
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>Высокий</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -13598,7 +15212,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>iskusstvo-legkogo-obshheniia-ot-nelovkix-pauz-k-besede-na-li</t>
+          <t>фридман александр - пожиратели времени как избавить от лишне</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -13608,7 +15222,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Практическое пособие по small talk</t>
+          <t>Фридман — признанный эксперт по управленческому тайм-менеджменту</t>
         </is>
       </c>
     </row>
@@ -13616,29 +15230,29 @@
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Нет</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>kak-razgovarivat-s-kem-ugodno-uverennoe-obshhenie-v-liuboi-s</t>
+          <t>12 недель в году</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>16:02 книга</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Практическое пособие по уверенному общению</t>
+          <t>Мур/Снайдер — известная методология квартального планирования [из истории проекта]</t>
         </is>
       </c>
     </row>
@@ -13646,29 +15260,29 @@
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="C10" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>Высокий</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Нет</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>net-i-tocka-iskusstvo-govorit-net-bez-cuvstva-viny</t>
+          <t>Как работать 4 часа в неделю</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>22:22 книга</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Практическая тема личных границ</t>
+          <t>Тимоти Феррис — один из самых влиятельных бестселлеров по продуктивности [из истории проекта]</t>
         </is>
       </c>
     </row>
@@ -13688,7 +15302,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>гоулстон марк - умение слушать осознанно</t>
+          <t>legkii-sposob-perestat-otkladyvat-dela-na-potom</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -13698,7 +15312,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Гоулстон — дубль темы с книгой выше</t>
+          <t>Практическое пособие по прокрастинации</t>
         </is>
       </c>
     </row>
@@ -13718,7 +15332,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>демиденко артем - переговоры на грани как выигрывать сложные</t>
+          <t>pravila-produktivnosti-dlia-nevrotika-instrukciia-po-vyzivan</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -13728,7 +15342,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Демиденко — массовый автор, обзорная книга по переговорам</t>
+          <t>Нишевая тема для тревожных прокрастинаторов</t>
         </is>
       </c>
     </row>
@@ -13736,9 +15350,9 @@
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Низкий</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
@@ -13748,7 +15362,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>кинг патрик - как быть веселым остроумным и креативным</t>
+          <t>6880608</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -13758,37 +15372,37 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>Патрик Кинг — лёгкий практический жанр</t>
+          <t>Неопознанный файл на диске — нужно открыть и определить книгу</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="n">
+      <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>кинг патрик - справочник мастера харизмы 174 поведенческих п</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>Патрик Кинг — практический сборник приёмов харизмы</t>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>52 понедельника: Как за год добиться любых целей</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Джонсон Вик</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Годовое планирование по неделям [ваш список]</t>
         </is>
       </c>
     </row>
@@ -13797,13 +15411,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -13862,7 +15476,7 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>arhangelskii g- taim-draiv ipod</t>
+          <t>porter1</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
@@ -13872,7 +15486,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Глеб Архангельский — ключевое издание по тайм-менеджменту</t>
+          <t>Майкл Портер — классика стратегического менеджмента</t>
         </is>
       </c>
     </row>
@@ -13892,7 +15506,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>kak-privesti-dela-v-poriadok-iskusstvo-produktivnosti-bez-st</t>
+          <t>sam-sebe-mba-samoobrazovanie-na-100</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -13902,7 +15516,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Дэвид Аллен — главная книга по системе GTD</t>
+          <t>Джош Кауфман — популярный синтез ключевых бизнес-концепций</t>
         </is>
       </c>
     </row>
@@ -13922,7 +15536,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>kak-razobratsia-s-delami</t>
+          <t>вумек-д.п.-дэниел-т.д.-бережливое-производство.-как-избавить</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -13932,7 +15546,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Дэвид Аллен — ещё одно издание GTD</t>
+          <t>Вумек/Джонс — основополагающая книга по Lean</t>
         </is>
       </c>
     </row>
@@ -13952,7 +15566,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>архангельский глеб - время большая книга тайм-менеджмента</t>
+          <t>когнитивно-бихевиоральная терапия психических расстройств, я</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -13962,7 +15576,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Глеб Архангельский — главный русскоязычный автор темы</t>
+          <t>Прашко — авторитетное клиническое руководство по КПТ</t>
         </is>
       </c>
     </row>
@@ -13975,24 +15589,24 @@
           <t>Высокий</t>
         </is>
       </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Нет</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>архангельский глеб - организация времени от личной эффективн</t>
+          <t>Карьера Менеджера</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ли Якокка</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Архангельский — расширенная версия методологии</t>
+          <t>Ли Якокка — классика автобиографического менеджмента [ваш список]</t>
         </is>
       </c>
     </row>
@@ -14000,9 +15614,9 @@
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>Высокий</t>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -14012,7 +15626,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>фрайд джейсон - не сходите с ума на работе</t>
+          <t>kak-delat-milliony-na-ideiax-rukovodstvo-dlia-predprinimatel</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -14022,7 +15636,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>Джейсон Фрайд — влиятельная книга о фокусе в работе</t>
+          <t>Практический жанр для стартаперов</t>
         </is>
       </c>
     </row>
@@ -14030,29 +15644,29 @@
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="B8" s="3" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Нет</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>фридман александр - пожиратели времени как избавить от лишне</t>
+          <t>Бизнес с нуля</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>23:33 книга</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Фридман — признанный эксперт по управленческому тайм-менеджменту</t>
+          <t>Общий практический курс для начинающих предпринимателей [из истории проекта]</t>
         </is>
       </c>
     </row>
@@ -14060,9 +15674,9 @@
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
-      <c r="B9" s="3" t="inlineStr">
-        <is>
-          <t>Высокий</t>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -14072,17 +15686,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12 недель в году</t>
+          <t>Малый бизнес:от иллюзий к успеху</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16:02 книга</t>
+          <t>31:34 книга</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>Мур/Снайдер — известная методология квартального планирования [из истории проекта]</t>
+          <t>Практический курс малого бизнеса [из истории проекта]</t>
         </is>
       </c>
     </row>
@@ -14090,9 +15704,9 @@
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
-      <c r="B10" s="3" t="inlineStr">
-        <is>
-          <t>Высокий</t>
+      <c r="B10" s="6" t="inlineStr">
+        <is>
+          <t>Средний</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -14102,17 +15716,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Как работать 4 часа в неделю</t>
+          <t>Наука управлять людьми</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22:22 книга</t>
+          <t>Ю. И. Мухин</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>Тимоти Феррис — один из самых влиятельных бестселлеров по продуктивности [из истории проекта]</t>
+          <t>Мухин — специфичный авторский взгляд на управление [ваш список]</t>
         </is>
       </c>
     </row>
@@ -14120,9 +15734,9 @@
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
-      <c r="B11" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>Низкий</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -14132,7 +15746,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>legkii-sposob-perestat-otkladyvat-dela-na-potom</t>
+          <t>короткий с - терминаторный менеджмент</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -14142,7 +15756,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Практическое пособие по прокрастинации</t>
+          <t>С. Короткий — малоизвестный автор, юмористический жанр</t>
         </is>
       </c>
     </row>
@@ -14150,443 +15764,329 @@
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="C12" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>Низкий</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Нет</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>pravila-produktivnosti-dlia-nevrotika-instrukciia-po-vyzivan</t>
+          <t>Путешествие из демократии в дерьмократию и дорога обратно</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Ю. И. Мухин</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Нишевая тема для тревожных прокрастинаторов</t>
+          <t>Политико-публицистический, не деловой жанр [ваш список]</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="n">
+      <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>6880608</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>Неопознанный файл на диске — нужно открыть и определить книгу</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F12"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
-    <col width="65" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>№</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Приоритет</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Статус</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Книга</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Автор</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Почему / комментарий</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>Высокий</t>
         </is>
       </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>porter1</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Майкл Портер — классика стратегического менеджмента</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Сделано, чтобы прилипать. Почему одни идеи выживают, а другие умирают</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Хиз Чип, Хиз Дэн</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Классика о запоминающихся идеях (Made to Stick) [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Маркетинг от потребителя</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Роджер Бест</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Маркетинг, ориентированный на потребителя [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Высокий</t>
         </is>
       </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>sam-sebe-mba-samoobrazovanie-na-100</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Джош Кауфман — популярный синтез ключевых бизнес-концепций</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>вумек-д.п.-дэниел-т.д.-бережливое-производство.-как-избавить</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Вумек/Джонс — основополагающая книга по Lean</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>когнитивно-бихевиоральная терапия психических расстройств, я</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Прашко — авторитетное клиническое руководство по КПТ</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
-        <is>
-          <t>Высокий</t>
-        </is>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Карьера Менеджера</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>Ли Якокка</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Ли Якокка — классика автобиографического менеджмента [ваш список]</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>kak-delat-milliony-na-ideiax-rukovodstvo-dlia-predprinimatel</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Практический жанр для стартаперов</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="C8" s="5" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Бизнес с нуля</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>23:33 книга</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Общий практический курс для начинающих предпринимателей [из истории проекта]</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Малый бизнес:от иллюзий к успеху</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>31:34 книга</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Практический курс малого бизнеса [из истории проекта]</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="6" t="inlineStr">
-        <is>
-          <t>Средний</t>
-        </is>
-      </c>
-      <c r="C10" s="5" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Наука управлять людьми</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>Ю. И. Мухин</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Мухин — специфичный авторский взгляд на управление [ваш список]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>Есть</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>короткий с - терминаторный менеджмент</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>С. Короткий — малоизвестный автор, юмористический жанр</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="n">
-        <v>11</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>Низкий</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Путешествие из демократии в дерьмократию и дорога обратно</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Ю. И. Мухин</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Политико-публицистический, не деловой жанр [ваш список]</t>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Позиционирование: битва за умы</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Траут Джек, Райс А.</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Классика маркетинга о позиционировании [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Дифференцируйся или умирай! Маркетинг и продвижение</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Траут Джек, Ривкин Стив</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Траут — дифференциация в маркетинге [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Маркетинговые войны</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Траут Джек, Райс А.</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Траут/Райс — маркетинг как военные действия [ваш список; входит в комплект с «Позиционированием» и «Дифференцируйся»]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Метод McKinsey: как решить любую проблему</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Расиел Итан М.</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Методология McKinsey [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MBA в картинках: Два года бизнес-школы в одной книге</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Бэррон Джейсон</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Визуальный обзор MBA [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Книга пяти колец</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Миямото Мусаси</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Классика стратегии, применима к бизнесу [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>ChatGPT на каждый день: 333 промта для бизнеса и маркетинга</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Халилов Дамир</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Промпты для бизнеса [ваш список]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Средний</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ChatGPT. Мастер подсказок или Как создавать сильные промпты для нейросети</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Панда Петр, Сычева Арина</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Практика промптов [ваш список]</t>
         </is>
       </c>
     </row>
